--- a/plantillas/plantilla_procesos.xlsx
+++ b/plantillas/plantilla_procesos.xlsx
@@ -26,20 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,7 +57,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,86 +425,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>FECHA INICIO</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FECHA INICIO</t>
+          <t>CLIENTE</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>CLIENTE</t>
+          <t>SUBCLIENTE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SUBCLIENTE</t>
+          <t>TIPO DE PROCESO</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TIPO DE PROCESO</t>
+          <t>CIUDAD</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD</t>
+          <t>CEDULA</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CEDULA</t>
+          <t>NOMBRE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>NOMBRE</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>FECHA FINALIZACION</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>FECHA FINALIZACION</t>
+          <t>ESTADO</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>ESTADO</t>
+          <t>FACTURA</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ORDEN DE COMPRA</t>
         </is>
@@ -510,65 +507,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>ALMACENES EXITO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALMACENES EXITO</t>
+          <t>BODEGA NORTE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BODEGA NORTE</t>
+          <t>SELECCION</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SELECCION</t>
+          <t>MEDELLIN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MEDELLIN</t>
+          <t>1017234567</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1017234567</t>
+          <t>JUAN PEREZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JUAN PEREZ</t>
+          <t>AUXILIAR LOGISTICO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUXILIAR LOGISTICO</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FINALIZADO</t>
+          <t>FA-1001</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>FA-1001</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>OC-5510</t>
         </is>
